--- a/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026_DEER_GENERAL_SEASON_PRIVATE_LANDS.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026_DEER_GENERAL_SEASON_PRIVATE_LANDS.xlsx
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -535,6 +535,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -598,10 +599,15 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Average Harvest Age Prior Year</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
+          <t>Average Harvest Age</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Current Age (3-Yr Avg)</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>Avg Days Hunted Prior Year</t>
         </is>
@@ -657,7 +663,8 @@
         </is>
       </c>
       <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -709,7 +716,8 @@
       </c>
       <c r="L5" s="6" t="inlineStr"/>
       <c r="M5" s="6" t="inlineStr"/>
-      <c r="N5" s="6" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" s="6" t="inlineStr"/>
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -761,7 +769,8 @@
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
@@ -813,7 +822,8 @@
       </c>
       <c r="L7" s="6" t="inlineStr"/>
       <c r="M7" s="6" t="inlineStr"/>
-      <c r="N7" s="6" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" s="6" t="inlineStr"/>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -861,7 +871,8 @@
       </c>
       <c r="L8" s="4" t="inlineStr"/>
       <c r="M8" s="4" t="inlineStr"/>
-      <c r="N8" s="4" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" s="4" t="inlineStr"/>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
@@ -913,7 +924,8 @@
         </is>
       </c>
       <c r="M9" s="6" t="inlineStr"/>
-      <c r="N9" s="6" t="inlineStr">
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -965,7 +977,8 @@
       </c>
       <c r="L10" s="4" t="inlineStr"/>
       <c r="M10" s="4" t="inlineStr"/>
-      <c r="N10" s="4" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" s="4" t="inlineStr"/>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
@@ -1013,7 +1026,8 @@
       </c>
       <c r="L11" s="6" t="inlineStr"/>
       <c r="M11" s="6" t="inlineStr"/>
-      <c r="N11" s="6" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" s="6" t="inlineStr"/>
     </row>
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
@@ -1065,7 +1079,8 @@
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr"/>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" s="4" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
@@ -1117,7 +1132,8 @@
       </c>
       <c r="L13" s="6" t="inlineStr"/>
       <c r="M13" s="6" t="inlineStr"/>
-      <c r="N13" s="6" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" s="6" t="inlineStr"/>
     </row>
     <row r="14" ht="32" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
@@ -1165,7 +1181,8 @@
       </c>
       <c r="L14" s="4" t="inlineStr"/>
       <c r="M14" s="4" t="inlineStr"/>
-      <c r="N14" s="4" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" s="4" t="inlineStr"/>
     </row>
     <row r="15" ht="32" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
@@ -1217,7 +1234,8 @@
         </is>
       </c>
       <c r="M15" s="6" t="inlineStr"/>
-      <c r="N15" s="6" t="inlineStr">
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" s="6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -1273,7 +1291,8 @@
         </is>
       </c>
       <c r="M16" s="4" t="inlineStr"/>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" s="4" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
@@ -1325,7 +1344,8 @@
       </c>
       <c r="L17" s="6" t="inlineStr"/>
       <c r="M17" s="6" t="inlineStr"/>
-      <c r="N17" s="6" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" s="6" t="inlineStr"/>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
@@ -1373,7 +1393,8 @@
       </c>
       <c r="L18" s="4" t="inlineStr"/>
       <c r="M18" s="4" t="inlineStr"/>
-      <c r="N18" s="4" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" s="4" t="inlineStr"/>
     </row>
     <row r="19" ht="32" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
@@ -1421,7 +1442,8 @@
       </c>
       <c r="L19" s="6" t="inlineStr"/>
       <c r="M19" s="6" t="inlineStr"/>
-      <c r="N19" s="6" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" s="6" t="inlineStr"/>
     </row>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
@@ -1473,7 +1495,8 @@
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr"/>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" s="4" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
